--- a/RELACION MOVCON - APRRINT (2).xlsx
+++ b/RELACION MOVCON - APRRINT (2).xlsx
@@ -5,17 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x16268\Desktop\IBK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/spachasn_proveedor_intercorp_com_pe/Documents/1. IBK/9. Modelo de Datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{521ACF1A-EBA2-44C1-9357-FFA073D7336F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1490" documentId="8_{24A603A0-C53B-4B2C-A542-EB2752778485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9273D1B-49D6-4387-8489-70665E74A108}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="708" activeTab="1" xr2:uid="{E781E287-5D13-4BD9-BF6A-910B21DB4CBA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="708" activeTab="3" xr2:uid="{E781E287-5D13-4BD9-BF6A-910B21DB4CBA}"/>
   </bookViews>
   <sheets>
     <sheet name="INDICE" sheetId="2" r:id="rId1"/>
-    <sheet name="COMPARATIVA" sheetId="5" r:id="rId2"/>
-    <sheet name="Cantidad_registros" sheetId="4" state="hidden" r:id="rId3"/>
+    <sheet name="COMPARATIVA" sheetId="5" state="hidden" r:id="rId2"/>
+    <sheet name="APR30.04 VS MOV30.04" sheetId="6" r:id="rId3"/>
+    <sheet name="APR30.04 VS MOVMES01.04-30.04" sheetId="7" r:id="rId4"/>
+    <sheet name="Cantidad_registros" sheetId="4" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">COMPARATIVA!$A$2:$N$16</definedName>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="181">
   <si>
     <t>TABLA</t>
   </si>
@@ -238,9 +240,6 @@
   </si>
   <si>
     <t>CCD</t>
-  </si>
-  <si>
-    <t>PENDIENTE ACCESO A ESTA TABLA POR PARTE DE IBK</t>
   </si>
   <si>
     <t>RNT.T_APRRINT_WBC_TMP</t>
@@ -679,9 +678,6 @@
     <t>CANTIDAD DE OPERACIONES QUE SE ENCUENTRAN EN MOVCON Y NO EN APR</t>
   </si>
   <si>
-    <t>TOTAL MOVCON</t>
-  </si>
-  <si>
     <t xml:space="preserve">select * 
 from( SELECT SUBSTR(FM_CLAVE_CUENTA, 1, 22) AS FM_CLAVE_CUENTA_NUEVO
         FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='$IM'  
@@ -693,6 +689,494 @@
     GROUP BY P01_ID_DOCU
 ) APR
 on MOV.FM_CLAVE_CUENTA_NUEVO = APR.P01_ID_DOCU </t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>% Total</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT FM_CLAVE_CUENTA AS FM_CONCATENADO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='SCF'  --AND FM_EFF_FECHA = '30-APR-26'
+AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+--GROUP BY FM_CLAVE_CUENTA
+) MOV
+FULL join (
+    SELECT P01_ID_CAMP_01,P01_CTRL03,	APRRMTX_ID_CLAV_01,	APRRMTX_ID_CLAV_02,substr(P01_NU_DOCU,3,8) as p01_nu_docu,	substr(p01_ctrl02,2,3) as moneda,	P01_ID_DOCU --AS P01_CONCATENADO
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'SCF' 
+--GROUP BY P01_ID_CAMP_01,P01_CTRL03,	APRRMTX_ID_CLAV_01,	APRRMTX_ID_CLAV_02, p01_nu_docu, p01_ctrl02, P01_ID_DOCU
+) APR
+--on MOV.FM_CONCATENADO = APR.P01_CONCATENADO
+ON FM_CONCATENADO= P01_ID_CAMP_01|| ' '|| P01_CTRL03|| APRRMTX_ID_CLAV_01|| ' '|| APRRMTX_ID_CLAV_02|| ' '|| P01_NU_DOCU|| moneda|| P01_ID_DOCU
+) TABA
+--WHERE (P01_ID_CAMP_01|| ' '|| P01_CTRL03|| APRRMTX_ID_CLAV_01|| ' '|| APRRMTX_ID_CLAV_02|| ' '|| P01_NU_DOCU|| moneda|| P01_ID_DOCU ) = '   ' 
+--WHERE TABA.P01_CONCATENADO IS NULL 
+--WHERE TABA.FM_CONCATENADO IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT FM_CLAVE_CUENTA AS FM_CONCATENADO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='SCF'  AND FM_EFF_FECHA = '30-APR-26'
+--AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+--GROUP BY FM_CLAVE_CUENTA
+) MOV
+FULL join (
+    SELECT P01_ID_CAMP_01,P01_CTRL03,	APRRMTX_ID_CLAV_01,	APRRMTX_ID_CLAV_02,substr(P01_NU_DOCU,3,8) as p01_nu_docu,	substr(p01_ctrl02,2,3) as moneda,	P01_ID_DOCU --AS P01_CONCATENADO
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'SCF' 
+--GROUP BY P01_ID_CAMP_01,P01_CTRL03,	APRRMTX_ID_CLAV_01,	APRRMTX_ID_CLAV_02, p01_nu_docu, p01_ctrl02, P01_ID_DOCU
+) APR
+--on MOV.FM_CONCATENADO = APR.P01_CONCATENADO
+ON FM_CONCATENADO= P01_ID_CAMP_01|| ' '|| P01_CTRL03|| APRRMTX_ID_CLAV_01|| ' '|| APRRMTX_ID_CLAV_02|| ' '|| P01_NU_DOCU|| moneda|| P01_ID_DOCU
+) TABA
+--WHERE (P01_ID_CAMP_01|| ' '|| P01_CTRL03|| APRRMTX_ID_CLAV_01|| ' '|| APRRMTX_ID_CLAV_02|| ' '|| P01_NU_DOCU|| moneda|| P01_ID_DOCU ) = '   ' 
+--WHERE TABA.P01_CONCATENADO IS NULL 
+--WHERE TABA.FM_CONCATENADO IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT '00'||substr(FM_CLAVE_CUENTA,5,8) AS FM_CONCATENADO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='HPC'  AND FM_EFF_FECHA = '30-APR-26'
+--AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY '00'||substr(FM_CLAVE_CUENTA,5,8)
+) MOV
+left join (
+    SELECT P01_NU_DOCU AS P01_CONCATENADO
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'HPC' 
+GROUP BY P01_NU_DOCU
+) APR
+on MOV.FM_CONCATENADO = APR.P01_CONCATENADO
+) TABA
+WHERE TABA.P01_CONCATENADO IS NULL 
+--WHERE TABA.FM_CONCATENADO IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT '00'||substr(FM_CLAVE_CUENTA,5,8) AS FM_CONCATENADO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='HPC'  --AND FM_EFF_FECHA = '30-APR-26'
+AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY '00'||substr(FM_CLAVE_CUENTA,5,8)
+) MOV
+left join (
+    SELECT P01_NU_DOCU AS P01_CONCATENADO
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'HPC' 
+GROUP BY P01_NU_DOCU
+) APR
+on MOV.FM_CONCATENADO = APR.P01_CONCATENADO
+) TABA
+WHERE TABA.P01_CONCATENADO IS NULL 
+--WHERE TABA.FM_CONCATENADO IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT substr(FM_CLAVE_CUENTA,1,10) AS FM_CONCATENADO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='FCD'  --AND FM_EFF_FECHA = '30-APR-26'
+AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY substr(FM_CLAVE_CUENTA,1,10)
+) MOV
+INNER join (
+    SELECT P01_NU_DOCU AS P01_CONCATENADO
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'FCD' 
+GROUP BY P01_NU_DOCU
+) APR
+on MOV.FM_CONCATENADO = APR.P01_CONCATENADO
+) TABA
+--WHERE TABA.P01_CONCATENADO IS NULL 
+--WHERE TABA.FM_CONCATENADO IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT substr(FM_CLAVE_CUENTA,1,10) AS FM_CONCATENADO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='FCD'  AND FM_EFF_FECHA = '30-APR-26'
+--AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY substr(FM_CLAVE_CUENTA,1,10)
+) MOV
+INNER join (
+    SELECT P01_NU_DOCU AS P01_CONCATENADO
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'FCD' 
+GROUP BY P01_NU_DOCU
+) APR
+on MOV.FM_CONCATENADO = APR.P01_CONCATENADO
+) TABA
+--WHERE TABA.P01_CONCATENADO IS NULL 
+--WHERE TABA.FM_CONCATENADO IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT REPLACE(substr(FM_CLAVE_CUENTA,13,18), ' ', '') AS FM_CONCATENADO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='CDO'  --AND FM_EFF_FECHA = '30-APR-26'
+AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY REPLACE(substr(FM_CLAVE_CUENTA,13,18), ' ', '')
+) MOV
+INNER join (
+    SELECT P01_NU_TARJ_CRED AS P01_CONCATENADO
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'CDO' 
+GROUP BY P01_NU_TARJ_CRED
+) APR
+on MOV.FM_CONCATENADO = APR.P01_CONCATENADO
+) TABA
+--WHERE TABA.P01_CONCATENADO IS NULL 
+--WHERE TABA.FM_CONCATENADO IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT REPLACE(substr(FM_CLAVE_CUENTA,13,18), ' ', '') AS FM_CONCATENADO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='CDO'  AND FM_EFF_FECHA = '30-APR-26'
+--AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY REPLACE(substr(FM_CLAVE_CUENTA,13,18), ' ', '')
+) MOV
+INNER join (
+    SELECT P01_NU_TARJ_CRED AS P01_CONCATENADO
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'CDO' 
+GROUP BY P01_NU_TARJ_CRED
+) APR
+on MOV.FM_CONCATENADO = APR.P01_CONCATENADO
+) TABA
+--WHERE TABA.P01_CONCATENADO IS NULL 
+--WHERE TABA.FM_CONCATENADO IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT  SUBSTR(FM_CLAVE_CUENTA, 24,8) AS FM_CONCATENADO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='MYP'  --AND FM_EFF_FECHA = '30-APR-26' 
+AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY  SUBSTR(FM_CLAVE_CUENTA, 24,8)
+) MOV
+INNER join (
+SELECT SUBSTR(P01_NU_DOCU,3,8) AS P01_CONCATENADO
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'MYP'
+GROUP BY SUBSTR(P01_NU_DOCU,3,8)
+) APR
+on MOV.FM_CONCATENADO = APR.P01_CONCATENADO 
+) TABA
+--WHERE TABA.P01_CONCATENADO IS NULL 
+--WHERE TABA.FM_CONCATENADO IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT  SUBSTR(FM_CLAVE_CUENTA, 24,8) AS FM_CONCATENADO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='MYP'  AND FM_EFF_FECHA = '30-APR-26' 
+--AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY  SUBSTR(FM_CLAVE_CUENTA, 24,8)
+) MOV
+INNER join (
+SELECT SUBSTR(P01_NU_DOCU,3,8) AS P01_CONCATENADO
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'MYP'
+GROUP BY SUBSTR(P01_NU_DOCU,3,8)
+) APR
+on MOV.FM_CONCATENADO = APR.P01_CONCATENADO 
+) TABA
+--WHERE TABA.P01_CONCATENADO IS NULL 
+--WHERE TABA.FM_CONCATENADO IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT  substr(REPLACE(FM_CLAVE_CUENTA, ' ', ''),1,28) AS FM_CONCATENADO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='LPC'  AND FM_EFF_FECHA = '30-APR-26' 
+--AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY  substr(REPLACE(FM_CLAVE_CUENTA, ' ', ''),1,28)
+) MOV
+INNER join (
+SELECT P01_ID_CAMP_01,substr(P01_CTRL02,2,3) as p01_ctrl02,	substr(p01_ctrl03,2,3) as p01_ctrl03	,P01_ID_CAMP_02,	P01_ID_CAMP_03	,P01_CO_PROD_ORIG,	substr(P01_NU_DOCU,3,8) as p01_nu_docu --AS P01_CONCATENADO
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'LPC'
+GROUP BY P01_ID_CAMP_01,substr(P01_CTRL02,2,3),	substr(p01_ctrl03,2,3)	,P01_ID_CAMP_02,	P01_ID_CAMP_03	,P01_CO_PROD_ORIG,	substr(P01_NU_DOCU,3,8)
+) APR
+on MOV.FM_CONCATENADO = P01_ID_CAMP_01||p01_ctrl02||p01_ctrl03||P01_ID_CAMP_02||P01_ID_CAMP_03||P01_CO_PROD_ORIG||p01_nu_docu 
+) TABA
+--WHERE TABA.P01_CONCATENADO IS NULL 
+--WHERE TABA.FM_CONCATENADO IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT  substr(REPLACE(FM_CLAVE_CUENTA, ' ', ''),1,28) AS FM_CONCATENADO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='LPC'  --AND FM_EFF_FECHA = '30-APR-26' 
+AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY  substr(REPLACE(FM_CLAVE_CUENTA, ' ', ''),1,28)
+) MOV
+INNER join (
+SELECT P01_ID_CAMP_01,substr(P01_CTRL02,2,3) as p01_ctrl02,	substr(p01_ctrl03,2,3) as p01_ctrl03	,P01_ID_CAMP_02,	P01_ID_CAMP_03	,P01_CO_PROD_ORIG,	substr(P01_NU_DOCU,3,8) as p01_nu_docu --AS P01_CONCATENADO
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'LPC'
+GROUP BY P01_ID_CAMP_01,substr(P01_CTRL02,2,3),	substr(p01_ctrl03,2,3)	,P01_ID_CAMP_02,	P01_ID_CAMP_03	,P01_CO_PROD_ORIG,	substr(P01_NU_DOCU,3,8)
+) APR
+on MOV.FM_CONCATENADO = P01_ID_CAMP_01||p01_ctrl02||p01_ctrl03||P01_ID_CAMP_02||P01_ID_CAMP_03||P01_CO_PROD_ORIG||p01_nu_docu 
+) TABA
+--WHERE TABA.P01_CONCATENADO IS NULL 
+--WHERE TABA.FM_CONCATENADO IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT SUBSTR(FM_CLAVE_CUENTA,1,22) AS FM_DOCUMENTO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='$IM' AND FM_EFF_FECHA = '30-APR-26' 
+--AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY SUBSTR(FM_CLAVE_CUENTA,1,22)
+) MOV
+ inner join (
+SELECT P01_ID_DOCU
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = '$IM'
+GROUP BY P01_ID_DOCU
+) APR
+on MOV.FM_DOCUMENTO = APR.P01_ID_DOCU 
+) TABA
+--WHERE TABA.P01_ID_DOCU IS NULL 
+--WHERE TABA.FM_DOCUMENTO IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT SUBSTR(FM_CLAVE_CUENTA,1,22) AS FM_DOCUMENTO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='$IM' --AND FM_EFF_FECHA = '30-APR-26' 
+AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY SUBSTR(FM_CLAVE_CUENTA,1,22)
+) MOV
+ inner join (
+SELECT P01_ID_DOCU
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = '$IM'
+GROUP BY P01_ID_DOCU
+) APR
+on MOV.FM_DOCUMENTO = APR.P01_ID_DOCU 
+) TABA
+--WHERE TABA.P01_ID_DOCU IS NULL 
+--WHERE TABA.FM_DOCUMENTO IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT  FM_CLAVE_CUENTA AS FM_LLAVE
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='$ST'  AND FM_EFF_FECHA = '30-APR-26' 
+--AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY  FM_CLAVE_CUENTA
+) MOV
+inner join (
+SELECT P01_ID_DOCU AS P01_LLAVE
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = '$ST'
+GROUP BY P01_ID_DOCU
+) APR
+on MOV.FM_LLAVE = APR.P01_LLAVE
+) TABA
+--WHERE TABA.P01_LLAVE IS NULL 
+--WHERE TABA.FM_LLAVE IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT  FM_CLAVE_CUENTA AS FM_LLAVE
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='$ST'  --AND FM_EFF_FECHA = '30-APR-26' 
+AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY  FM_CLAVE_CUENTA
+) MOV
+inner join (
+SELECT P01_ID_DOCU AS P01_LLAVE
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = '$ST'
+GROUP BY P01_ID_DOCU
+) APR
+on MOV.FM_LLAVE = APR.P01_LLAVE
+) TABA
+--WHERE TABA.P01_LLAVE IS NULL 
+--WHERE TABA.FM_LLAVE IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT  REPLACE(FM_CLAVE_CUENTA, ' ', '') AS FM_LLAVE
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='MDC'  AND FM_EFF_FECHA = '30-APR-26' 
+--AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY  REPLACE(FM_CLAVE_CUENTA, ' ', '')
+) MOV
+inner join (
+SELECT DWHRR_ESP_DISPONIBLE, REGEXP_REPLACE(P01_NU_DOCU, '1', '0', 1, 1) AS P01_NU_DOCU,REGEXP_REPLACE(P01_NU_CNTA, '1', '0', 1, 1) AS P01_NU_CNTA
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'MDC'
+GROUP BY DWHRR_ESP_DISPONIBLE, REGEXP_REPLACE(P01_NU_DOCU, '1', '0', 1, 1) ,REGEXP_REPLACE(P01_NU_CNTA, '1', '0', 1, 1)
+) APR
+on MOV.FM_LLAVE = DWHRR_ESP_DISPONIBLE||P01_NU_DOCU||P01_NU_CNTA
+) TABA
+--WHERE TABA.P01_LLAVE IS NULL 
+--WHERE DWHRR_ESP_DISPONIBLE IS NULL 
+--WHERE TABA.FM_LLAVE IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT  REPLACE(FM_CLAVE_CUENTA, ' ', '') AS FM_LLAVE
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='MDC'  --AND FM_EFF_FECHA = '30-APR-26' 
+AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY  REPLACE(FM_CLAVE_CUENTA, ' ', '')
+) MOV
+inner join (
+SELECT DWHRR_ESP_DISPONIBLE, REGEXP_REPLACE(P01_NU_DOCU, '1', '0', 1, 1) AS P01_NU_DOCU,REGEXP_REPLACE(P01_NU_CNTA, '1', '0', 1, 1) AS P01_NU_CNTA
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'MDC'
+GROUP BY DWHRR_ESP_DISPONIBLE, REGEXP_REPLACE(P01_NU_DOCU, '1', '0', 1, 1) ,REGEXP_REPLACE(P01_NU_CNTA, '1', '0', 1, 1)
+) APR
+on MOV.FM_LLAVE = DWHRR_ESP_DISPONIBLE||P01_NU_DOCU||P01_NU_CNTA
+) TABA
+--WHERE TABA.P01_LLAVE IS NULL 
+--WHERE DWHRR_ESP_DISPONIBLE IS NULL 
+--WHERE TABA.FM_LLAVE IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT  REPLACE(FM_CLAVE_CUENTA, ' ', '') AS FM_LLAVE
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='LIC'  --AND FM_EFF_FECHA = '30-APR-26' 
+AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY  REPLACE(FM_CLAVE_CUENTA, ' ', '')
+) MOV
+INNER join (
+SELECT P01_OF_ADMIN,	SUBSTR(P01_NU_DOCU,3,8) as p01_nu_docu1,	P01_CO_PROD_ORIG,	SUBSTR(P01_CTRL02,2,3) as p01_ctrl02,	P01_CTRL04,	SUBSTR(P01_CTRL12,2,3)	as P01_CTRL12,P01_CO_TIENDA_IC	,APRFCRO_DIAS_ATRA_MES as APRFCRO_DIAS_ATRA_MES1,	SUBSTR(P01_ID_CAMP_03,2,3) as p01_id_camp_03, APRFCRO_DIAS_ATRA_MES, SUBSTR(P01_NU_DOCU,4,4) as p01_nu_docu  
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'LIC'
+GROUP BY P01_OF_ADMIN,	SUBSTR(P01_NU_DOCU,3,8),	P01_CO_PROD_ORIG,	SUBSTR(P01_CTRL02,2,3),	P01_CTRL04,	SUBSTR(P01_CTRL12,2,3)	,P01_CO_TIENDA_IC	,APRFCRO_DIAS_ATRA_MES,	SUBSTR(P01_ID_CAMP_03,2,3), APRFCRO_DIAS_ATRA_MES, SUBSTR(P01_NU_DOCU,4,4) 
+) APR
+on MOV.FM_LLAVE = P01_OF_ADMIN||P01_NU_DOCU1||P01_CO_PROD_ORIG||P01_CTRL02||P01_CTRL04||P01_CTRL12||P01_CO_TIENDA_IC||APRFCRO_DIAS_ATRA_MES1||P01_ID_CAMP_03||APRFCRO_DIAS_ATRA_MES||P01_NU_DOCU
+) TABA
+--WHERE P01_OF_ADMIN IS NULL 
+--WHERE TABA.FM_LLAVE IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT  REPLACE(FM_CLAVE_CUENTA, ' ', '') AS FM_LLAVE
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='LIC'  AND FM_EFF_FECHA = '30-APR-26' 
+--AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY  REPLACE(FM_CLAVE_CUENTA, ' ', '')
+) MOV
+LEFT join (
+SELECT P01_OF_ADMIN,	SUBSTR(P01_NU_DOCU,3,8) as p01_nu_docu1,	P01_CO_PROD_ORIG,	SUBSTR(P01_CTRL02,2,3) as p01_ctrl02,	P01_CTRL04,	SUBSTR(P01_CTRL12,2,3)	as P01_CTRL12,P01_CO_TIENDA_IC	,APRFCRO_DIAS_ATRA_MES as APRFCRO_DIAS_ATRA_MES1,	SUBSTR(P01_ID_CAMP_03,2,3) as p01_id_camp_03, APRFCRO_DIAS_ATRA_MES, SUBSTR(P01_NU_DOCU,4,4) as p01_nu_docu  
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'LIC'
+GROUP BY P01_OF_ADMIN,	SUBSTR(P01_NU_DOCU,3,8),	P01_CO_PROD_ORIG,	SUBSTR(P01_CTRL02,2,3),	P01_CTRL04,	SUBSTR(P01_CTRL12,2,3)	,P01_CO_TIENDA_IC	,APRFCRO_DIAS_ATRA_MES,	SUBSTR(P01_ID_CAMP_03,2,3), APRFCRO_DIAS_ATRA_MES, SUBSTR(P01_NU_DOCU,4,4) 
+) APR
+on MOV.FM_LLAVE = P01_OF_ADMIN||P01_NU_DOCU1||P01_CO_PROD_ORIG||P01_CTRL02||P01_CTRL04||P01_CTRL12||P01_CO_TIENDA_IC||APRFCRO_DIAS_ATRA_MES1||P01_ID_CAMP_03||APRFCRO_DIAS_ATRA_MES||P01_NU_DOCU
+) TABA
+WHERE P01_OF_ADMIN IS NULL 
+--WHERE TABA.FM_LLAVE IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>RNT.T_APRRINT_CCD_TMP</t>
+  </si>
+  <si>
+    <t>NO VA. ANTIGUO APLICATIVO DE PROVISIONES, VIENE POR OTRA FUENTE QUE SE ESTA TRABAJANDO, FUENTE NUEVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	SOLO TIENE CUENTAS CONTABLES DE 8, SON DE ORDEN, NO SE UTILIZA EN RENTABILIDAD</t>
+  </si>
+  <si>
+    <t>NO TIENE CUENTA CONTABLE, Y NO TIENE SALDO, NO VA PARA EL SALDO DIARIO, PERO QUEDA LA DUDA SI PARA TRANSACTION DETAIL SE UTILIZA PPA (CONSULTAR MARTIN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SE NECESITA UN POCO MAS DE CONOCIMIENTO DE PARTE DE CONTABILIDAD, PARA PODER SABER SI ESTO SE OCUPA O NO </t>
+  </si>
+  <si>
+    <t>CORE DE CREDITOS DIGITAL</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT  substr(FM_CLAVE_CUENTA,35,45) AS FM_CONCATENADO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='CCD'  --AND FM_EFF_FECHA = '30-APR-26' 
+AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY  substr(FM_CLAVE_CUENTA,35,45)
+) MOV
+inner join (
+SELECT  P01_ID_DOCU AS P01_CONCATENADO
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'CCD'
+GROUP BY P01_ID_DOCU
+) APR
+on MOV.FM_CONCATENADO = APR.P01_CONCATENADO
+) TABA
+--WHERE TABA.P01_CONCATENADO IS NULL 
+--WHERE TABA.FM_CONCATENADO IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT  substr(FM_CLAVE_CUENTA,35,45) AS FM_CONCATENADO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='CCD'  AND FM_EFF_FECHA = '30-APR-26' 
+--AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY  substr(FM_CLAVE_CUENTA,35,45)
+) MOV
+inner join (
+SELECT  P01_ID_DOCU AS P01_CONCATENADO
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'CCD'
+GROUP BY P01_ID_DOCU
+) APR
+on MOV.FM_CONCATENADO = APR.P01_CONCATENADO
+) TABA
+--WHERE TABA.P01_CONCATENADO IS NULL 
+--WHERE TABA.FM_CONCATENADO IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT SUBSTR(REPLACE(FM_CLAVE_CUENTA, ' ', ''),1,32)  AS FM_CONCATENADO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='JCC' AND FM_EFF_FECHA = '30-APR-26'
+--AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY SUBSTR(REPLACE(FM_CLAVE_CUENTA, ' ', ''),1,32)
+) MOV
+right join (
+    SELECT P01_ID_APLI_DCMNTO AS P01_ID_APLI_DCMNTO1, SUBSTR(P01_NU_DOCU,3,8)as P01_NU_DOCU,	P01_ID_CAMP_01,	P01_ID_CAMP_02,	P01_ID_CAMP_03	,P01_ID_CAMP_04	,P01_ID_CAMP_05	,P01_ID_CAMP_06,	P01_ID_CAMP_07,	'CJ' --AS P01_CONCATENADO
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'JCC' AND TO_DATE(DWHRR_LAST_PAYMENT_DATE, 'YYYYMMDD') = DATE '2026-04-30'
+GROUP BY P01_ID_APLI_DCMNTO,SUBSTR(P01_NU_DOCU,3,8),	P01_ID_CAMP_01,	P01_ID_CAMP_02,	P01_ID_CAMP_03	,P01_ID_CAMP_04	,P01_ID_CAMP_05	,P01_ID_CAMP_06,	P01_ID_CAMP_07,	'CJ'
+) APR
+on MOV.FM_CONCATENADO = P01_ID_APLI_DCMNTO1||P01_NU_DOCU||P01_ID_CAMP_01||P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_CAMP_05||P01_ID_CAMP_06||P01_ID_CAMP_07||'CJ'
+) TABA
+--WHERE P01_ID_APLI_DCMNTO1 IS NULL
+--WHERE TABA.P01_CONCATENADO IS NULL 
+WHERE TABA.FM_CONCATENADO IS NULL 
+;</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM (
+select * 
+from( SELECT SUBSTR(REPLACE(FM_CLAVE_CUENTA, ' ', ''),1,32)  AS FM_CONCATENADO
+FROM RNT.T_INC_FMOVCON_TMP WHERE FM_APLICACION='JCC' --AND FM_EFF_FECHA = '30-APR-26'
+AND FM_EFF_FECHA &gt;= '01-APR-26' AND FM_EFF_FECHA &lt;= '30-APR-26'
+GROUP BY SUBSTR(REPLACE(FM_CLAVE_CUENTA, ' ', ''),1,32)
+) MOV
+RIGHT join (
+    SELECT P01_ID_APLI_DCMNTO AS P01_ID_APLI_DCMNTO1, SUBSTR(P01_NU_DOCU,3,8)as P01_NU_DOCU,	P01_ID_CAMP_01,	P01_ID_CAMP_02,	P01_ID_CAMP_03	,P01_ID_CAMP_04	,P01_ID_CAMP_05	,P01_ID_CAMP_06,	P01_ID_CAMP_07,	'CJ' --AS P01_CONCATENADO
+FROM RNT.T_APRRINT_HIST_20260430 WHERE P01_ID_APLI = 'JCC' AND TO_DATE(DWHRR_LAST_PAYMENT_DATE, 'YYYYMMDD') &gt;= DATE '2026-04-01' AND TO_DATE(DWHRR_LAST_PAYMENT_DATE, 'YYYYMMDD') &lt;= DATE '2026-04-30'
+GROUP BY P01_ID_APLI_DCMNTO,SUBSTR(P01_NU_DOCU,3,8),	P01_ID_CAMP_01,	P01_ID_CAMP_02,	P01_ID_CAMP_03	,P01_ID_CAMP_04	,P01_ID_CAMP_05	,P01_ID_CAMP_06,	P01_ID_CAMP_07,	'CJ'
+) APR
+on MOV.FM_CONCATENADO = P01_ID_APLI_DCMNTO1||P01_NU_DOCU||P01_ID_CAMP_01||P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_CAMP_05||P01_ID_CAMP_06||P01_ID_CAMP_07||'CJ'
+) TABA
+--WHERE P01_ID_APLI_DCMNTO1 IS NULL
+--WHERE TABA.P01_CONCATENADO IS NULL 
+WHERE TABA.FM_CONCATENADO IS NULL 
+;</t>
   </si>
 </sst>
 </file>
@@ -788,7 +1272,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -822,6 +1306,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -901,7 +1403,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -993,7 +1495,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1020,51 +1521,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1073,9 +1529,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1084,7 +1537,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1096,13 +1548,143 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1253,6 +1835,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
+<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1587,7 +2173,7 @@
     <col min="6" max="6" width="14.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.26953125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.81640625" style="39" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="44" style="38" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="29" x14ac:dyDescent="0.35">
@@ -1782,7 +2368,7 @@
       <c r="B8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="65" t="s">
         <v>34</v>
       </c>
       <c r="D8" s="13" t="s">
@@ -1797,7 +2383,7 @@
       <c r="G8" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="58" t="s">
+      <c r="H8" s="69" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1808,7 +2394,7 @@
       <c r="B9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="51"/>
+      <c r="C9" s="66"/>
       <c r="D9" s="13" t="s">
         <v>35</v>
       </c>
@@ -1821,7 +2407,7 @@
       <c r="G9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H9" s="59"/>
+      <c r="H9" s="70"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
@@ -1856,7 +2442,7 @@
       <c r="B11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="65" t="s">
         <v>42</v>
       </c>
       <c r="D11" s="13" t="s">
@@ -1871,7 +2457,7 @@
       <c r="G11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="58" t="s">
+      <c r="H11" s="69" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1882,7 +2468,7 @@
       <c r="B12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="51"/>
+      <c r="C12" s="66"/>
       <c r="D12" s="13" t="s">
         <v>46</v>
       </c>
@@ -1895,7 +2481,7 @@
       <c r="G12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="59"/>
+      <c r="H12" s="70"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
@@ -1949,16 +2535,16 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>57</v>
+        <v>176</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>12</v>
@@ -1967,24 +2553,24 @@
         <v>12</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H15" s="15" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="16" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>58</v>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>60</v>
+        <v>56</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>57</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>12</v>
@@ -1992,52 +2578,54 @@
       <c r="F16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="11" t="s">
         <v>13</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="I16" s="40" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="12" t="s">
-        <v>51</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="16" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="37" t="s">
-        <v>64</v>
+        <v>59</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>60</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="1"/>
+      <c r="G17" s="15" t="s">
+        <v>13</v>
+      </c>
       <c r="H17" s="15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+      <c r="I17" s="39" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="C18" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="32" t="s">
         <v>66</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>67</v>
       </c>
       <c r="E18" s="33"/>
       <c r="F18" s="33"/>
@@ -2047,83 +2635,95 @@
       <c r="H18" s="35" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I18" s="38" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="31" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C19" s="30" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E19" s="33"/>
       <c r="F19" s="33"/>
-      <c r="G19" s="34" t="s">
-        <v>51</v>
-      </c>
+      <c r="G19" s="34"/>
       <c r="H19" s="35" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A20" s="31" t="s">
+      <c r="I19" s="38" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="93"/>
+      <c r="F20" s="93"/>
+      <c r="G20" s="94" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" s="95" t="s">
+        <v>51</v>
+      </c>
+      <c r="I20" s="38" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="58" x14ac:dyDescent="0.35">
+      <c r="A21" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="34" t="s">
+      <c r="C21" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="93"/>
+      <c r="F21" s="93"/>
+      <c r="G21" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="H20" s="35" t="s">
+      <c r="H21" s="95" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A21" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="B21" s="30" t="s">
+      <c r="I21" s="38" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="35" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A22" s="27" t="s">
+      <c r="B22" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="C22" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="28" t="s">
         <v>75</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>76</v>
       </c>
       <c r="E22" s="29"/>
       <c r="F22" s="29"/>
@@ -2134,18 +2734,18 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="26" t="s">
-        <v>78</v>
-      </c>
       <c r="C23" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E23" s="29"/>
       <c r="F23" s="29"/>
@@ -2156,15 +2756,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="8" t="s">
@@ -2178,15 +2778,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="8" t="s">
@@ -2200,15 +2800,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="8" t="s">
@@ -2222,15 +2822,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="8" t="s">
@@ -2244,15 +2844,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="8" t="s">
@@ -2266,15 +2866,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="8" t="s">
@@ -2288,15 +2888,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D30" s="13"/>
       <c r="E30" s="8" t="s">
@@ -2310,15 +2910,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="8" t="s">
@@ -2332,15 +2932,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
         <v>51</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="8" t="s">
@@ -2359,10 +2959,10 @@
         <v>51</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D33" s="13"/>
       <c r="E33" s="8" t="s">
@@ -2381,10 +2981,10 @@
         <v>51</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D34" s="13"/>
       <c r="E34" s="8" t="s">
@@ -2403,10 +3003,10 @@
         <v>51</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D35" s="13"/>
       <c r="E35" s="8" t="s">
@@ -2425,10 +3025,10 @@
         <v>51</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D36" s="13"/>
       <c r="E36" s="8" t="s">
@@ -2447,10 +3047,10 @@
         <v>51</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D37" s="13"/>
       <c r="E37" s="8" t="s">
@@ -2469,10 +3069,10 @@
         <v>51</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D38" s="13"/>
       <c r="E38" s="8" t="s">
@@ -2491,10 +3091,10 @@
         <v>51</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D39" s="13"/>
       <c r="E39" s="8" t="s">
@@ -2513,10 +3113,10 @@
         <v>51</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D40" s="13"/>
       <c r="E40" s="8" t="s">
@@ -2535,10 +3135,10 @@
         <v>51</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D41" s="13"/>
       <c r="E41" s="8" t="s">
@@ -2557,10 +3157,10 @@
         <v>51</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D42" s="13"/>
       <c r="E42" s="8" t="s">
@@ -2579,10 +3179,10 @@
         <v>51</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D43" s="13"/>
       <c r="E43" s="8" t="s">
@@ -2601,10 +3201,10 @@
         <v>51</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="8" t="s">
@@ -2671,14 +3271,14 @@
     <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:F44" xr:uid="{6213ED68-F7EE-4E61-BE52-FED917530AE8}">
-      <formula1>"Si, No"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H10:H11 H2:H8 H13:H17" xr:uid="{6AAF00AE-AC21-472D-A9A7-72A42448EE88}">
+      <formula1>"Validado, En Proceso, Pendiente, -"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H18:H44" xr:uid="{9729A518-218B-42F0-8B33-05C522CB8837}">
       <formula1>"Validado, Incidencia, Pendiente, -"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H13:H17 H2:H8 H10:H11" xr:uid="{6AAF00AE-AC21-472D-A9A7-72A42448EE88}">
-      <formula1>"Validado, En Proceso, Pendiente, -"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E18:F44 E2:F17" xr:uid="{6213ED68-F7EE-4E61-BE52-FED917530AE8}">
+      <formula1>"Si, No"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2691,35 +3291,36 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="42.1796875" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" customWidth="1"/>
     <col min="5" max="5" width="28.1796875" customWidth="1"/>
     <col min="6" max="6" width="29" customWidth="1"/>
     <col min="7" max="7" width="26.7265625" customWidth="1"/>
     <col min="8" max="8" width="17.7265625" customWidth="1"/>
     <col min="9" max="9" width="22.1796875" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="19" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="14" style="70" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="14" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="12.26953125" customWidth="1"/>
     <col min="13" max="14" width="12.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
+      <c r="A1" s="64" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
     </row>
     <row r="2" spans="1:16" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
@@ -2729,55 +3330,58 @@
         <v>1</v>
       </c>
       <c r="C2" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="19" t="s">
-        <v>103</v>
-      </c>
       <c r="E2" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2" s="20" t="s">
         <v>147</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>148</v>
       </c>
       <c r="H2" s="25" t="s">
         <v>149</v>
       </c>
       <c r="I2" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="K2" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="L2" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="J2" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="K2" s="66" t="s">
-        <v>142</v>
-      </c>
-      <c r="L2" s="25" t="s">
+      <c r="M2" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="N2" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="N2" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="P2" s="47"/>
+      <c r="O2" s="75" t="s">
+        <v>150</v>
+      </c>
+      <c r="P2" s="46"/>
     </row>
     <row r="3" spans="1:16" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="83" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" s="23">
         <v>162</v>
@@ -2788,25 +3392,29 @@
       <c r="G3" s="23">
         <v>16</v>
       </c>
-      <c r="H3" s="75">
+      <c r="H3" s="57">
         <v>5332</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J3" s="23"/>
       <c r="K3" s="23"/>
-      <c r="L3" s="46">
-        <f>IFERROR(1-(E3/H3),"-")</f>
-        <v>0.96961740435108779</v>
-      </c>
-      <c r="M3" s="41">
-        <f>IFERROR(F3/H3,"-")</f>
+      <c r="L3" s="45">
+        <f>IFERROR((E3/H3),"-")</f>
+        <v>3.0382595648912228E-2</v>
+      </c>
+      <c r="M3" s="40">
+        <f t="shared" ref="M3:M9" si="0">IFERROR(F3/H3,"-")</f>
         <v>0.96661665416354092</v>
       </c>
-      <c r="N3" s="41">
-        <f>IFERROR(1-(G3/H3),"-")</f>
-        <v>0.99699924981245314</v>
+      <c r="N3" s="40">
+        <f>IFERROR((G3/H3),"-")</f>
+        <v>3.0007501875468868E-3</v>
+      </c>
+      <c r="O3" s="76">
+        <f>SUM(L3:N3)</f>
+        <v>1</v>
       </c>
       <c r="P3" s="18"/>
     </row>
@@ -2814,14 +3422,14 @@
       <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="89" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E4" s="23">
         <v>489416</v>
@@ -2832,26 +3440,30 @@
       <c r="G4" s="23">
         <v>659248</v>
       </c>
-      <c r="H4" s="75">
+      <c r="H4" s="57">
         <f>SUM(E4:G4)</f>
         <v>1186244</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J4" s="23"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="46">
-        <f t="shared" ref="L4:L15" si="0">IFERROR(1-(E4/H4),"-")</f>
-        <v>0.58742383523120034</v>
-      </c>
-      <c r="M4" s="41">
-        <f>IFERROR(F4/H4,"-")</f>
+      <c r="K4" s="50"/>
+      <c r="L4" s="45">
+        <f t="shared" ref="L4:L15" si="1">IFERROR((E4/H4),"-")</f>
+        <v>0.41257616476879966</v>
+      </c>
+      <c r="M4" s="40">
+        <f t="shared" si="0"/>
         <v>3.1679823038093344E-2</v>
       </c>
-      <c r="N4" s="41">
-        <f t="shared" ref="N4:N15" si="1">IFERROR(1-(G4/H4),"-")</f>
-        <v>0.44425598780689302</v>
+      <c r="N4" s="40">
+        <f t="shared" ref="N4:N15" si="2">IFERROR((G4/H4),"-")</f>
+        <v>0.55574401219310698</v>
+      </c>
+      <c r="O4" s="76">
+        <f t="shared" ref="O4:O15" si="3">SUM(L4:N4)</f>
+        <v>1</v>
       </c>
       <c r="P4" s="22"/>
     </row>
@@ -2859,14 +3471,14 @@
       <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="89" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E5" s="23">
         <v>188334</v>
@@ -2877,39 +3489,43 @@
       <c r="G5" s="23">
         <v>522</v>
       </c>
-      <c r="H5" s="75">
+      <c r="H5" s="57">
         <v>70014</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J5" s="23"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="46">
+      <c r="K5" s="50"/>
+      <c r="L5" s="45">
+        <f t="shared" si="1"/>
+        <v>2.6899477247407662</v>
+      </c>
+      <c r="M5" s="40">
         <f t="shared" si="0"/>
-        <v>-1.6899477247407662</v>
-      </c>
-      <c r="M5" s="41">
-        <f>IFERROR(F5/H5,"-")</f>
         <v>0.99254434827320248</v>
       </c>
-      <c r="N5" s="41">
-        <f t="shared" si="1"/>
-        <v>0.99254434827320248</v>
+      <c r="N5" s="40">
+        <f t="shared" si="2"/>
+        <v>7.4556517267974978E-3</v>
+      </c>
+      <c r="O5" s="76">
+        <f t="shared" si="3"/>
+        <v>3.6899477247407662</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="83" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E6" s="23">
         <v>1890</v>
@@ -2920,40 +3536,44 @@
       <c r="G6" s="23">
         <v>109</v>
       </c>
-      <c r="H6" s="75">
+      <c r="H6" s="57">
         <f>SUM(E6:G6)</f>
         <v>23443</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J6" s="23"/>
       <c r="K6" s="23"/>
-      <c r="L6" s="46">
+      <c r="L6" s="45">
+        <f t="shared" si="1"/>
+        <v>8.0621080919677512E-2</v>
+      </c>
+      <c r="M6" s="40">
         <f t="shared" si="0"/>
-        <v>0.91937891908032254</v>
-      </c>
-      <c r="M6" s="41">
-        <f>IFERROR(F6/H6,"-")</f>
         <v>0.91472934351405533</v>
       </c>
-      <c r="N6" s="41">
-        <f t="shared" si="1"/>
-        <v>0.99535042443373289</v>
+      <c r="N6" s="40">
+        <f t="shared" si="2"/>
+        <v>4.6495755662671161E-3</v>
+      </c>
+      <c r="O6" s="76">
+        <f t="shared" si="3"/>
+        <v>0.99999999999999989</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="89" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>28</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E7" s="23">
         <v>794</v>
@@ -2964,39 +3584,43 @@
       <c r="G7" s="23">
         <v>1099</v>
       </c>
-      <c r="H7" s="75">
+      <c r="H7" s="57">
         <v>3283</v>
       </c>
-      <c r="I7" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="J7" s="42"/>
-      <c r="K7" s="68"/>
-      <c r="L7" s="46">
+      <c r="I7" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="J7" s="41"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="45">
+        <f t="shared" si="1"/>
+        <v>0.24185196466646361</v>
+      </c>
+      <c r="M7" s="40">
         <f t="shared" si="0"/>
-        <v>0.75814803533353636</v>
-      </c>
-      <c r="M7" s="41">
-        <f>IFERROR(F7/H7,"-")</f>
         <v>0.42339323789217181</v>
       </c>
-      <c r="N7" s="41">
-        <f t="shared" si="1"/>
-        <v>0.6652452025586354</v>
+      <c r="N7" s="40">
+        <f t="shared" si="2"/>
+        <v>0.3347547974413646</v>
+      </c>
+      <c r="O7" s="76">
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="83" t="s">
         <v>30</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="43" t="s">
-        <v>115</v>
+      <c r="D8" s="42" t="s">
+        <v>114</v>
       </c>
       <c r="E8" s="23">
         <v>318</v>
@@ -3007,102 +3631,111 @@
       <c r="G8" s="23">
         <v>109</v>
       </c>
-      <c r="H8" s="75">
+      <c r="H8" s="57">
         <v>6729</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J8" s="23"/>
       <c r="K8" s="23"/>
-      <c r="L8" s="46">
+      <c r="L8" s="45">
+        <f t="shared" si="1"/>
+        <v>4.7258136424431565E-2</v>
+      </c>
+      <c r="M8" s="40">
         <f t="shared" si="0"/>
-        <v>0.95274186357556845</v>
-      </c>
-      <c r="M8" s="41">
-        <f>IFERROR(F8/H8,"-")</f>
         <v>0.93654331995838902</v>
       </c>
-      <c r="N8" s="41">
-        <f t="shared" si="1"/>
-        <v>0.98380145638282057</v>
+      <c r="N8" s="40">
+        <f t="shared" si="2"/>
+        <v>1.6198543617179373E-2</v>
+      </c>
+      <c r="O8" s="76">
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="90" t="s">
         <v>34</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="56" t="s">
+      <c r="D9" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" s="60">
+        <v>441111</v>
+      </c>
+      <c r="F9" s="60">
+        <v>115630</v>
+      </c>
+      <c r="G9" s="60">
+        <v>931</v>
+      </c>
+      <c r="H9" s="62">
+        <v>557672</v>
+      </c>
+      <c r="I9" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="E9" s="61">
-        <v>441111</v>
-      </c>
-      <c r="F9" s="61">
-        <v>115630</v>
-      </c>
-      <c r="G9" s="61">
-        <v>931</v>
-      </c>
-      <c r="H9" s="77">
-        <v>557672</v>
-      </c>
-      <c r="I9" s="73" t="s">
-        <v>118</v>
-      </c>
-      <c r="J9" s="63"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="48">
+      <c r="J9" s="47"/>
+      <c r="K9" s="52"/>
+      <c r="L9" s="58">
+        <f t="shared" si="1"/>
+        <v>0.79098645798964262</v>
+      </c>
+      <c r="M9" s="58">
         <f t="shared" si="0"/>
-        <v>0.20901354201035738</v>
-      </c>
-      <c r="M9" s="48">
-        <f>IFERROR(F9/H9,"-")</f>
         <v>0.20734410190936609</v>
       </c>
-      <c r="N9" s="48">
-        <f t="shared" si="1"/>
-        <v>0.99833055989900876</v>
+      <c r="N9" s="58">
+        <f t="shared" si="2"/>
+        <v>1.6694401009912636E-3</v>
+      </c>
+      <c r="O9" s="78">
+        <f t="shared" si="3"/>
+        <v>0.99999999999999989</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="51"/>
+      <c r="B10" s="66"/>
       <c r="C10" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="57"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="78"/>
-      <c r="I10" s="73"/>
-      <c r="J10" s="64"/>
-      <c r="K10" s="64"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
-      <c r="N10" s="49"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="59"/>
+      <c r="M10" s="59"/>
+      <c r="N10" s="59"/>
+      <c r="O10" s="79"/>
     </row>
     <row r="11" spans="1:16" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="88" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>39</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E11" s="23">
         <v>59</v>
@@ -3113,103 +3746,112 @@
       <c r="G11" s="23">
         <v>44</v>
       </c>
-      <c r="H11" s="75">
+      <c r="H11" s="57">
         <f>SUM(E11:G11)</f>
         <v>715</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J11" s="23"/>
       <c r="K11" s="23"/>
-      <c r="L11" s="44">
-        <f t="shared" si="0"/>
-        <v>0.91748251748251752</v>
-      </c>
-      <c r="M11" s="44">
+      <c r="L11" s="45">
+        <f t="shared" si="1"/>
+        <v>8.2517482517482518E-2</v>
+      </c>
+      <c r="M11" s="43">
         <f>IFERROR(F11/H11,"-")</f>
         <v>0.85594405594405598</v>
       </c>
-      <c r="N11" s="44">
-        <f t="shared" si="1"/>
-        <v>0.93846153846153846</v>
+      <c r="N11" s="40">
+        <f t="shared" si="2"/>
+        <v>6.1538461538461542E-2</v>
+      </c>
+      <c r="O11" s="76">
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="87" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="72" t="s">
-        <v>121</v>
-      </c>
-      <c r="E12" s="61">
+      <c r="D12" s="54" t="s">
+        <v>120</v>
+      </c>
+      <c r="E12" s="60">
         <v>12703</v>
       </c>
-      <c r="F12" s="61">
+      <c r="F12" s="60">
         <v>181808</v>
       </c>
-      <c r="G12" s="61">
+      <c r="G12" s="60">
         <v>1306</v>
       </c>
-      <c r="H12" s="77">
+      <c r="H12" s="62">
         <v>195817</v>
       </c>
-      <c r="I12" s="74" t="s">
-        <v>112</v>
-      </c>
-      <c r="J12" s="65"/>
-      <c r="K12" s="65"/>
-      <c r="L12" s="48">
-        <f t="shared" si="0"/>
-        <v>0.93512820643764327</v>
-      </c>
-      <c r="M12" s="48">
+      <c r="I12" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="J12" s="49"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="58">
+        <f t="shared" si="1"/>
+        <v>6.4871793562356686E-2</v>
+      </c>
+      <c r="M12" s="58">
         <f>IFERROR(F12/SUM(E12:G12),"-")</f>
         <v>0.92845871400338076</v>
       </c>
-      <c r="N12" s="48">
-        <f t="shared" si="1"/>
-        <v>0.99333050756573738</v>
+      <c r="N12" s="58">
+        <f t="shared" si="2"/>
+        <v>6.6694924342626024E-3</v>
+      </c>
+      <c r="O12" s="78">
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="51"/>
+      <c r="B13" s="66"/>
       <c r="C13" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D13" s="43"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="64"/>
-      <c r="K13" s="64"/>
-      <c r="L13" s="49"/>
-      <c r="M13" s="49"/>
-      <c r="N13" s="49"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="59"/>
+      <c r="M13" s="59"/>
+      <c r="N13" s="59"/>
+      <c r="O13" s="79"/>
     </row>
     <row r="14" spans="1:16" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="83" t="s">
         <v>53</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>54</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E14" s="23">
         <v>25793</v>
@@ -3220,39 +3862,43 @@
       <c r="G14" s="23">
         <v>8382</v>
       </c>
-      <c r="H14" s="75">
+      <c r="H14" s="57">
         <v>132037</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J14" s="23"/>
       <c r="K14" s="23"/>
-      <c r="L14" s="46">
-        <f t="shared" si="0"/>
-        <v>0.80465324113695402</v>
-      </c>
-      <c r="M14" s="41">
+      <c r="L14" s="45">
+        <f t="shared" si="1"/>
+        <v>0.19534675886304598</v>
+      </c>
+      <c r="M14" s="40">
         <f>IFERROR(F14/H14,"-")</f>
         <v>0.74117103539159479</v>
       </c>
-      <c r="N14" s="41">
-        <f t="shared" si="1"/>
-        <v>0.93651779425464077</v>
+      <c r="N14" s="40">
+        <f t="shared" si="2"/>
+        <v>6.348220574535926E-2</v>
+      </c>
+      <c r="O14" s="76">
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="83" t="s">
         <v>56</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>57</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E15" s="23">
         <v>329</v>
@@ -3263,29 +3909,33 @@
       <c r="G15" s="23">
         <v>553</v>
       </c>
-      <c r="H15" s="75">
+      <c r="H15" s="57">
         <v>100868</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J15" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="K15" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="K15" s="71" t="s">
-        <v>144</v>
-      </c>
-      <c r="L15" s="46">
-        <f t="shared" si="0"/>
-        <v>0.99673831145655711</v>
-      </c>
-      <c r="M15" s="41">
+      <c r="L15" s="45">
+        <f t="shared" si="1"/>
+        <v>3.2616885434429157E-3</v>
+      </c>
+      <c r="M15" s="40">
         <f>IFERROR(F15/H15,"-")</f>
         <v>0.99125589879842968</v>
       </c>
-      <c r="N15" s="41">
-        <f t="shared" si="1"/>
-        <v>0.99451758734187257</v>
+      <c r="N15" s="40">
+        <f t="shared" si="2"/>
+        <v>5.4824126581274535E-3</v>
+      </c>
+      <c r="O15" s="76">
+        <f t="shared" si="3"/>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="29" x14ac:dyDescent="0.35">
@@ -3306,18 +3956,19 @@
       <c r="I16" s="23"/>
       <c r="J16" s="23"/>
       <c r="K16" s="23"/>
-      <c r="L16" s="45" t="str">
+      <c r="L16" s="44" t="str">
         <f>IFERROR(G16/H16,"-")</f>
         <v>-</v>
       </c>
-      <c r="M16" s="44" t="str">
+      <c r="M16" s="43" t="str">
         <f>IFERROR(F16/H16,"-")</f>
         <v>-</v>
       </c>
-      <c r="N16" s="44" t="str">
+      <c r="N16" s="43" t="str">
         <f>IFERROR(E16/H16,"-")</f>
         <v>-</v>
       </c>
+      <c r="O16" s="1"/>
     </row>
     <row r="17" spans="5:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="E17" s="18"/>
@@ -3328,15 +3979,11 @@
     <row r="20" spans="5:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <autoFilter ref="A2:N16" xr:uid="{8830F8C7-80D5-4680-8632-11F7E9D2B088}"/>
-  <mergeCells count="18">
-    <mergeCell ref="M12:M13"/>
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="A1:N1"/>
+  <mergeCells count="20">
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="O12:O13"/>
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="L9:L10"/>
@@ -3346,8 +3993,26 @@
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="D9:D10"/>
-    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="L12:L13"/>
   </mergeCells>
+  <conditionalFormatting sqref="L3:L9 L14:L15 L11:L12">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="70"/>
+        <cfvo type="percent" val="100"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M3:M9 M11:M12 M14:M16">
     <cfRule type="colorScale" priority="3">
       <colorScale>
@@ -3360,19 +4025,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L3:L9 L11:L12 L14:L15">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="70"/>
-        <cfvo type="percent" val="100"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N9 N11:N12 N14:N15">
+  <conditionalFormatting sqref="N3:N9 N14:N15 N11:N12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="percent" val="0"/>
@@ -3390,6 +4043,1499 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9FDD41E-4700-4992-B7D8-27B4D030FACC}">
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="10.90625" style="16"/>
+    <col min="3" max="3" width="41" style="16" customWidth="1"/>
+    <col min="4" max="4" width="10.90625" style="16"/>
+    <col min="5" max="5" width="34.36328125" style="16" customWidth="1"/>
+    <col min="6" max="6" width="26.26953125" style="16" customWidth="1"/>
+    <col min="7" max="7" width="34.36328125" style="16" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" style="16"/>
+    <col min="9" max="9" width="33" style="16" customWidth="1"/>
+    <col min="10" max="16384" width="10.90625" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="64" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+    </row>
+    <row r="2" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="M2" s="75" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3" s="55">
+        <v>156</v>
+      </c>
+      <c r="F3" s="55">
+        <v>5297</v>
+      </c>
+      <c r="G3" s="55">
+        <v>22</v>
+      </c>
+      <c r="H3" s="97">
+        <f>SUM(E3:G3)</f>
+        <v>5475</v>
+      </c>
+      <c r="I3" s="56" t="s">
+        <v>139</v>
+      </c>
+      <c r="J3" s="43">
+        <f>IFERROR((E3/H3),"-")</f>
+        <v>2.8493150684931506E-2</v>
+      </c>
+      <c r="K3" s="98">
+        <f>IFERROR(F3/H3,"-")</f>
+        <v>0.96748858447488584</v>
+      </c>
+      <c r="L3" s="98">
+        <f>IFERROR((G3/H3),"-")</f>
+        <v>4.018264840182648E-3</v>
+      </c>
+      <c r="M3" s="99">
+        <f>SUM(J3:L3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="80" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" s="55">
+        <v>23106490</v>
+      </c>
+      <c r="F4" s="55">
+        <v>790783</v>
+      </c>
+      <c r="G4" s="55">
+        <v>209</v>
+      </c>
+      <c r="H4" s="97">
+        <f t="shared" ref="H4:H17" si="0">SUM(E4:G4)</f>
+        <v>23897482</v>
+      </c>
+      <c r="I4" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="J4" s="43">
+        <f>IFERROR((E4/H4),"-")</f>
+        <v>0.96690061321104881</v>
+      </c>
+      <c r="K4" s="98">
+        <f>IFERROR(F4/H4,"-")</f>
+        <v>3.3090641097668787E-2</v>
+      </c>
+      <c r="L4" s="98">
+        <f>IFERROR((G4/H4),"-")</f>
+        <v>8.7456912824539431E-6</v>
+      </c>
+      <c r="M4" s="99">
+        <f t="shared" ref="M4:M15" si="1">SUM(J4:L4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E5" s="55">
+        <v>240694</v>
+      </c>
+      <c r="F5" s="55">
+        <v>17133</v>
+      </c>
+      <c r="G5" s="55">
+        <v>0</v>
+      </c>
+      <c r="H5" s="97">
+        <f t="shared" si="0"/>
+        <v>257827</v>
+      </c>
+      <c r="I5" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="J5" s="43">
+        <f>IFERROR((E5/H5),"-")</f>
+        <v>0.93354846466816899</v>
+      </c>
+      <c r="K5" s="98">
+        <f>IFERROR(F5/H5,"-")</f>
+        <v>6.6451535331831041E-2</v>
+      </c>
+      <c r="L5" s="98">
+        <f>IFERROR((G5/H5),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="99">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="80" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E6" s="55">
+        <v>1873</v>
+      </c>
+      <c r="F6" s="55">
+        <v>21461</v>
+      </c>
+      <c r="G6" s="55">
+        <v>49</v>
+      </c>
+      <c r="H6" s="97">
+        <f t="shared" si="0"/>
+        <v>23383</v>
+      </c>
+      <c r="I6" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="J6" s="43">
+        <f>IFERROR((E6/H6),"-")</f>
+        <v>8.0100928024633283E-2</v>
+      </c>
+      <c r="K6" s="98">
+        <f>IFERROR(F6/H6,"-")</f>
+        <v>0.91780353248086222</v>
+      </c>
+      <c r="L6" s="98">
+        <f>IFERROR((G6/H6),"-")</f>
+        <v>2.0955394945045545E-3</v>
+      </c>
+      <c r="M6" s="99">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="80" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E7" s="55">
+        <v>535</v>
+      </c>
+      <c r="F7" s="55">
+        <v>1649</v>
+      </c>
+      <c r="G7" s="55">
+        <v>861</v>
+      </c>
+      <c r="H7" s="97">
+        <f t="shared" si="0"/>
+        <v>3045</v>
+      </c>
+      <c r="I7" s="100" t="s">
+        <v>113</v>
+      </c>
+      <c r="J7" s="43">
+        <f>IFERROR((E7/H7),"-")</f>
+        <v>0.17569786535303777</v>
+      </c>
+      <c r="K7" s="98">
+        <f>IFERROR(F7/H7,"-")</f>
+        <v>0.54154351395730704</v>
+      </c>
+      <c r="L7" s="98">
+        <f>IFERROR((G7/H7),"-")</f>
+        <v>0.28275862068965518</v>
+      </c>
+      <c r="M7" s="99">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="87" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="80" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="80" t="s">
+        <v>161</v>
+      </c>
+      <c r="E8" s="55">
+        <v>187</v>
+      </c>
+      <c r="F8" s="55">
+        <v>6433</v>
+      </c>
+      <c r="G8" s="55">
+        <v>57</v>
+      </c>
+      <c r="H8" s="97">
+        <f t="shared" si="0"/>
+        <v>6677</v>
+      </c>
+      <c r="I8" s="56" t="s">
+        <v>115</v>
+      </c>
+      <c r="J8" s="43">
+        <f>IFERROR((E8/H8),"-")</f>
+        <v>2.800658978583196E-2</v>
+      </c>
+      <c r="K8" s="98">
+        <f>IFERROR(F8/H8,"-")</f>
+        <v>0.96345664220458294</v>
+      </c>
+      <c r="L8" s="98">
+        <f>IFERROR((G8/H8),"-")</f>
+        <v>8.5367680095851436E-3</v>
+      </c>
+      <c r="M8" s="99">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="80" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="E9" s="60">
+        <v>440652</v>
+      </c>
+      <c r="F9" s="60">
+        <v>116089</v>
+      </c>
+      <c r="G9" s="60">
+        <v>651</v>
+      </c>
+      <c r="H9" s="84">
+        <f t="shared" si="0"/>
+        <v>557392</v>
+      </c>
+      <c r="I9" s="81" t="s">
+        <v>117</v>
+      </c>
+      <c r="J9" s="58">
+        <f>IFERROR((E9/H9),"-")</f>
+        <v>0.7905603237936677</v>
+      </c>
+      <c r="K9" s="58">
+        <f>IFERROR(F9/H9,"-")</f>
+        <v>0.20827173694635015</v>
+      </c>
+      <c r="L9" s="58">
+        <f>IFERROR((G9/H9),"-")</f>
+        <v>1.1679392599822029E-3</v>
+      </c>
+      <c r="M9" s="78">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="66"/>
+      <c r="C10" s="80" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="68"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="82"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
+      <c r="L10" s="59"/>
+      <c r="M10" s="79"/>
+    </row>
+    <row r="11" spans="1:13" ht="116" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="80" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="101" t="s">
+        <v>179</v>
+      </c>
+      <c r="E11" s="55">
+        <v>110</v>
+      </c>
+      <c r="F11" s="55">
+        <v>1147</v>
+      </c>
+      <c r="G11" s="55">
+        <v>24</v>
+      </c>
+      <c r="H11" s="86">
+        <f t="shared" si="0"/>
+        <v>1281</v>
+      </c>
+      <c r="I11" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="J11" s="43">
+        <f>IFERROR((E11/H11),"-")</f>
+        <v>8.5870413739266196E-2</v>
+      </c>
+      <c r="K11" s="43">
+        <f>IFERROR(F11/H11,"-")</f>
+        <v>0.89539422326307572</v>
+      </c>
+      <c r="L11" s="98">
+        <f>IFERROR((G11/H11),"-")</f>
+        <v>1.873536299765808E-2</v>
+      </c>
+      <c r="M11" s="99">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="102" t="s">
+        <v>153</v>
+      </c>
+      <c r="E12" s="60">
+        <v>10590</v>
+      </c>
+      <c r="F12" s="60">
+        <v>183921</v>
+      </c>
+      <c r="G12" s="60">
+        <v>922</v>
+      </c>
+      <c r="H12" s="84">
+        <f t="shared" si="0"/>
+        <v>195433</v>
+      </c>
+      <c r="I12" s="81" t="s">
+        <v>111</v>
+      </c>
+      <c r="J12" s="58">
+        <f>IFERROR((E12/H12),"-")</f>
+        <v>5.4187368561092547E-2</v>
+      </c>
+      <c r="K12" s="58">
+        <f>IFERROR(F12/SUM(E12:G12),"-")</f>
+        <v>0.9410949020892071</v>
+      </c>
+      <c r="L12" s="58">
+        <f>IFERROR((G12/H12),"-")</f>
+        <v>4.7177293497004088E-3</v>
+      </c>
+      <c r="M12" s="78">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="66"/>
+      <c r="C13" s="80" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="104"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="85"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="59"/>
+      <c r="L13" s="59"/>
+      <c r="M13" s="79"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="80" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E14" s="55">
+        <v>18227</v>
+      </c>
+      <c r="F14" s="55">
+        <v>105428</v>
+      </c>
+      <c r="G14" s="55">
+        <v>1490</v>
+      </c>
+      <c r="H14" s="97">
+        <f t="shared" si="0"/>
+        <v>125145</v>
+      </c>
+      <c r="I14" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="J14" s="43">
+        <f>IFERROR((E14/H14),"-")</f>
+        <v>0.14564704942266971</v>
+      </c>
+      <c r="K14" s="98">
+        <f>IFERROR(F14/H14,"-")</f>
+        <v>0.84244676175636257</v>
+      </c>
+      <c r="L14" s="98">
+        <f>IFERROR((G14/H14),"-")</f>
+        <v>1.1906188820967677E-2</v>
+      </c>
+      <c r="M14" s="99">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="58" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="80" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E15" s="55">
+        <v>494</v>
+      </c>
+      <c r="F15" s="55">
+        <v>99821</v>
+      </c>
+      <c r="G15" s="55">
+        <v>401</v>
+      </c>
+      <c r="H15" s="97">
+        <f t="shared" si="0"/>
+        <v>100716</v>
+      </c>
+      <c r="I15" s="56" t="s">
+        <v>144</v>
+      </c>
+      <c r="J15" s="43">
+        <f>IFERROR((E15/H15),"-")</f>
+        <v>4.9048810516700422E-3</v>
+      </c>
+      <c r="K15" s="98">
+        <f>IFERROR(F15/H15,"-")</f>
+        <v>0.99111362643472734</v>
+      </c>
+      <c r="L15" s="98">
+        <f>IFERROR((G15/H15),"-")</f>
+        <v>3.9814925136026054E-3</v>
+      </c>
+      <c r="M15" s="99">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="80" t="s">
+        <v>176</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E16" s="55">
+        <v>0</v>
+      </c>
+      <c r="F16" s="55">
+        <v>19</v>
+      </c>
+      <c r="G16" s="55">
+        <v>0</v>
+      </c>
+      <c r="H16" s="97">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="I16" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="J16" s="43">
+        <f>IFERROR((E16/H16),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="98">
+        <f>IFERROR(F16/H16,"-")</f>
+        <v>1</v>
+      </c>
+      <c r="L16" s="98">
+        <f>IFERROR((G16/H16),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="99">
+        <f t="shared" ref="M16" si="2">SUM(J16:L16)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="97">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="55"/>
+      <c r="J17" s="44" t="str">
+        <f>IFERROR(G17/H17,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="K17" s="43" t="str">
+        <f>IFERROR(F17/H17,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="L17" s="43" t="str">
+        <f>IFERROR(E17/H17,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="M17" s="101"/>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L9:L10"/>
+  </mergeCells>
+  <conditionalFormatting sqref="J3:L17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="70"/>
+        <cfvo type="percent" val="100"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96BC16D0-932C-4A67-B414-BA66D4631AA7}">
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="10.90625" style="16"/>
+    <col min="3" max="3" width="38.36328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.90625" style="16"/>
+    <col min="5" max="5" width="34.36328125" style="16" customWidth="1"/>
+    <col min="6" max="6" width="26.26953125" style="16" customWidth="1"/>
+    <col min="7" max="7" width="34.36328125" style="16" customWidth="1"/>
+    <col min="8" max="8" width="11.6328125" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43.6328125" style="16" customWidth="1"/>
+    <col min="10" max="16384" width="10.90625" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A1" s="64" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+    </row>
+    <row r="2" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="M2" s="75" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="58" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" s="55">
+        <v>64</v>
+      </c>
+      <c r="F3" s="55">
+        <v>104655</v>
+      </c>
+      <c r="G3" s="55">
+        <v>1299</v>
+      </c>
+      <c r="H3" s="97">
+        <f>SUM(E3:G3)</f>
+        <v>106018</v>
+      </c>
+      <c r="I3" s="56" t="s">
+        <v>139</v>
+      </c>
+      <c r="J3" s="43">
+        <f>IFERROR((E3/H3),"-")</f>
+        <v>6.0367107472316024E-4</v>
+      </c>
+      <c r="K3" s="98">
+        <f>IFERROR(F3/H3,"-")</f>
+        <v>0.98714369258050516</v>
+      </c>
+      <c r="L3" s="98">
+        <f>IFERROR((G3/H3),"-")</f>
+        <v>1.2252636344771643E-2</v>
+      </c>
+      <c r="M3" s="99">
+        <f>SUM(J3:L3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="80" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="E4" s="55">
+        <v>22785531</v>
+      </c>
+      <c r="F4" s="55">
+        <v>1111742</v>
+      </c>
+      <c r="G4" s="55">
+        <v>13899</v>
+      </c>
+      <c r="H4" s="97">
+        <f t="shared" ref="H4:H17" si="0">SUM(E4:G4)</f>
+        <v>23911172</v>
+      </c>
+      <c r="I4" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="J4" s="43">
+        <f>IFERROR((E4/H4),"-")</f>
+        <v>0.95292405575101047</v>
+      </c>
+      <c r="K4" s="98">
+        <f>IFERROR(F4/H4,"-")</f>
+        <v>4.649466784815065E-2</v>
+      </c>
+      <c r="L4" s="98">
+        <f>IFERROR((G4/H4),"-")</f>
+        <v>5.8127640083890496E-4</v>
+      </c>
+      <c r="M4" s="99">
+        <f t="shared" ref="M4:M16" si="1">SUM(J4:L4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E5" s="55">
+        <v>182727</v>
+      </c>
+      <c r="F5" s="55">
+        <v>75099</v>
+      </c>
+      <c r="G5" s="55">
+        <v>560</v>
+      </c>
+      <c r="H5" s="97">
+        <f t="shared" si="0"/>
+        <v>258386</v>
+      </c>
+      <c r="I5" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="J5" s="43">
+        <f>IFERROR((E5/H5),"-")</f>
+        <v>0.70718614785630796</v>
+      </c>
+      <c r="K5" s="98">
+        <f>IFERROR(F5/H5,"-")</f>
+        <v>0.29064655205777401</v>
+      </c>
+      <c r="L5" s="98">
+        <f>IFERROR((G5/H5),"-")</f>
+        <v>2.1673000859179677E-3</v>
+      </c>
+      <c r="M5" s="99">
+        <f t="shared" si="1"/>
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="80" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6" s="55">
+        <v>618</v>
+      </c>
+      <c r="F6" s="55">
+        <v>22716</v>
+      </c>
+      <c r="G6" s="55">
+        <v>838</v>
+      </c>
+      <c r="H6" s="97">
+        <f t="shared" si="0"/>
+        <v>24172</v>
+      </c>
+      <c r="I6" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="J6" s="43">
+        <f>IFERROR((E6/H6),"-")</f>
+        <v>2.5566771471123614E-2</v>
+      </c>
+      <c r="K6" s="98">
+        <f>IFERROR(F6/H6,"-")</f>
+        <v>0.9397650173754758</v>
+      </c>
+      <c r="L6" s="98">
+        <f>IFERROR((G6/H6),"-")</f>
+        <v>3.466821115340063E-2</v>
+      </c>
+      <c r="M6" s="99">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="80" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E7" s="55">
+        <v>535</v>
+      </c>
+      <c r="F7" s="55">
+        <v>1649</v>
+      </c>
+      <c r="G7" s="55">
+        <v>12684</v>
+      </c>
+      <c r="H7" s="97">
+        <f t="shared" si="0"/>
+        <v>14868</v>
+      </c>
+      <c r="I7" s="100" t="s">
+        <v>113</v>
+      </c>
+      <c r="J7" s="43">
+        <f>IFERROR((E7/H7),"-")</f>
+        <v>3.5983319881624967E-2</v>
+      </c>
+      <c r="K7" s="98">
+        <f>IFERROR(F7/H7,"-")</f>
+        <v>0.11090933548560668</v>
+      </c>
+      <c r="L7" s="98">
+        <f>IFERROR((G7/H7),"-")</f>
+        <v>0.85310734463276838</v>
+      </c>
+      <c r="M7" s="99">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="80" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="80" t="s">
+        <v>162</v>
+      </c>
+      <c r="E8" s="55">
+        <v>141</v>
+      </c>
+      <c r="F8" s="55">
+        <v>6479</v>
+      </c>
+      <c r="G8" s="55">
+        <v>1019</v>
+      </c>
+      <c r="H8" s="97">
+        <f t="shared" si="0"/>
+        <v>7639</v>
+      </c>
+      <c r="I8" s="56" t="s">
+        <v>115</v>
+      </c>
+      <c r="J8" s="43">
+        <f>IFERROR((E8/H8),"-")</f>
+        <v>1.8457913339442335E-2</v>
+      </c>
+      <c r="K8" s="98">
+        <f>IFERROR(F8/H8,"-")</f>
+        <v>0.84814766330671554</v>
+      </c>
+      <c r="L8" s="98">
+        <f>IFERROR((G8/H8),"-")</f>
+        <v>0.13339442335384213</v>
+      </c>
+      <c r="M8" s="99">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="80" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="91" t="s">
+        <v>169</v>
+      </c>
+      <c r="E9" s="60">
+        <v>417803</v>
+      </c>
+      <c r="F9" s="60">
+        <v>138938</v>
+      </c>
+      <c r="G9" s="60">
+        <v>8110</v>
+      </c>
+      <c r="H9" s="84">
+        <f t="shared" si="0"/>
+        <v>564851</v>
+      </c>
+      <c r="I9" s="81" t="s">
+        <v>117</v>
+      </c>
+      <c r="J9" s="58">
+        <f>IFERROR((E9/H9),"-")</f>
+        <v>0.73966939954076383</v>
+      </c>
+      <c r="K9" s="58">
+        <f>IFERROR(F9/H9,"-")</f>
+        <v>0.24597283177333493</v>
+      </c>
+      <c r="L9" s="58">
+        <f>IFERROR((G9/H9),"-")</f>
+        <v>1.4357768685901239E-2</v>
+      </c>
+      <c r="M9" s="78">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="66"/>
+      <c r="C10" s="80" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="92"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="82"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="59"/>
+      <c r="L10" s="59"/>
+      <c r="M10" s="79"/>
+    </row>
+    <row r="11" spans="1:13" ht="87" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="80" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="101" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" s="55">
+        <v>1828</v>
+      </c>
+      <c r="F11" s="55">
+        <v>9616</v>
+      </c>
+      <c r="G11" s="55">
+        <v>984</v>
+      </c>
+      <c r="H11" s="97">
+        <f t="shared" si="0"/>
+        <v>12428</v>
+      </c>
+      <c r="I11" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="J11" s="43">
+        <f>IFERROR((E11/H11),"-")</f>
+        <v>0.14708722240102992</v>
+      </c>
+      <c r="K11" s="43">
+        <f>IFERROR(F11/H11,"-")</f>
+        <v>0.77373672352751854</v>
+      </c>
+      <c r="L11" s="98">
+        <f>IFERROR((G11/H11),"-")</f>
+        <v>7.9176054071451563E-2</v>
+      </c>
+      <c r="M11" s="99">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="80" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="102" t="s">
+        <v>154</v>
+      </c>
+      <c r="E12" s="60">
+        <v>1228</v>
+      </c>
+      <c r="F12" s="60">
+        <v>193283</v>
+      </c>
+      <c r="G12" s="60">
+        <v>11072</v>
+      </c>
+      <c r="H12" s="84">
+        <f t="shared" si="0"/>
+        <v>205583</v>
+      </c>
+      <c r="I12" s="81" t="s">
+        <v>111</v>
+      </c>
+      <c r="J12" s="58">
+        <f>IFERROR((E12/H12),"-")</f>
+        <v>5.9732565435858019E-3</v>
+      </c>
+      <c r="K12" s="58">
+        <f>IFERROR(F12/SUM(E12:G12),"-")</f>
+        <v>0.94017015025561457</v>
+      </c>
+      <c r="L12" s="58">
+        <f>IFERROR((G12/H12),"-")</f>
+        <v>5.3856593200799677E-2</v>
+      </c>
+      <c r="M12" s="78">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="66"/>
+      <c r="C13" s="80" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="103"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="85"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="59"/>
+      <c r="L13" s="59"/>
+      <c r="M13" s="79"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="80" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E14" s="55">
+        <v>17954</v>
+      </c>
+      <c r="F14" s="55">
+        <v>105701</v>
+      </c>
+      <c r="G14" s="55">
+        <v>50162</v>
+      </c>
+      <c r="H14" s="97">
+        <f t="shared" si="0"/>
+        <v>173817</v>
+      </c>
+      <c r="I14" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="J14" s="43">
+        <f>IFERROR((E14/H14),"-")</f>
+        <v>0.10329254330704131</v>
+      </c>
+      <c r="K14" s="98">
+        <f>IFERROR(F14/H14,"-")</f>
+        <v>0.60811658238262079</v>
+      </c>
+      <c r="L14" s="98">
+        <f>IFERROR((G14/H14),"-")</f>
+        <v>0.28859087431033786</v>
+      </c>
+      <c r="M14" s="99">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="80" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E15" s="55">
+        <v>243</v>
+      </c>
+      <c r="F15" s="55">
+        <v>100072</v>
+      </c>
+      <c r="G15" s="55">
+        <v>9496</v>
+      </c>
+      <c r="H15" s="97">
+        <f t="shared" si="0"/>
+        <v>109811</v>
+      </c>
+      <c r="I15" s="56" t="s">
+        <v>144</v>
+      </c>
+      <c r="J15" s="43">
+        <f>IFERROR((E15/H15),"-")</f>
+        <v>2.2128930617151287E-3</v>
+      </c>
+      <c r="K15" s="98">
+        <f>IFERROR(F15/H15,"-")</f>
+        <v>0.91131125297101379</v>
+      </c>
+      <c r="L15" s="98">
+        <f>IFERROR((G15/H15),"-")</f>
+        <v>8.6475853967271032E-2</v>
+      </c>
+      <c r="M15" s="99">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="80" t="s">
+        <v>176</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E16" s="55">
+        <v>0</v>
+      </c>
+      <c r="F16" s="55">
+        <v>19</v>
+      </c>
+      <c r="G16" s="55">
+        <v>1</v>
+      </c>
+      <c r="H16" s="97">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="I16" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="J16" s="43">
+        <f>IFERROR((E16/H16),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="98">
+        <f>IFERROR(F16/H16,"-")</f>
+        <v>0.95</v>
+      </c>
+      <c r="L16" s="98">
+        <f>IFERROR((G16/H16),"-")</f>
+        <v>0.05</v>
+      </c>
+      <c r="M16" s="99">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="96" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="97">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="56"/>
+      <c r="J17" s="44" t="str">
+        <f>IFERROR(G17/H17,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="K17" s="43" t="str">
+        <f>IFERROR(F17/H17,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="L17" s="43" t="str">
+        <f>IFERROR(E17/H17,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="M17" s="101"/>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+  </mergeCells>
+  <conditionalFormatting sqref="J3:L15 J17:L17">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J16:L16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="70"/>
+        <cfvo type="percent" val="100"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25562D0C-D587-4E9B-A2E3-4DCE6D85EA31}">
   <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3403,12 +5549,12 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
       <c r="D1" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
@@ -3419,16 +5565,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D2" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="17" t="s">
         <v>127</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -3439,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D3" s="23">
         <v>5319</v>
@@ -3460,7 +5606,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D4" s="23">
         <v>700211</v>
@@ -3481,7 +5627,7 @@
         <v>21</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D5" s="23">
         <v>3383</v>
@@ -3502,7 +5648,7 @@
         <v>24</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D6" s="23">
         <v>22355</v>
@@ -3522,8 +5668,8 @@
       <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="38" t="s">
-        <v>133</v>
+      <c r="C7" s="37" t="s">
+        <v>132</v>
       </c>
       <c r="D7" s="23"/>
       <c r="E7" s="23"/>
@@ -3540,7 +5686,7 @@
         <v>30</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D8" s="23">
         <v>6963</v>
@@ -3557,19 +5703,19 @@
       <c r="A9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="57" t="s">
-        <v>135</v>
-      </c>
-      <c r="D9" s="54">
+      <c r="C9" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="71">
         <v>117263</v>
       </c>
-      <c r="E9" s="54">
+      <c r="E9" s="71">
         <v>903497</v>
       </c>
-      <c r="F9" s="60">
+      <c r="F9" s="72">
         <f t="shared" si="0"/>
         <v>786234</v>
       </c>
@@ -3578,11 +5724,11 @@
       <c r="A10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="51"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="60"/>
+      <c r="B10" s="66"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="72"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
@@ -3592,7 +5738,7 @@
         <v>38</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D11" s="23">
         <v>760</v>
@@ -3609,19 +5755,19 @@
       <c r="A12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="D12" s="54">
+      <c r="C12" s="73" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" s="71">
         <v>272609</v>
       </c>
-      <c r="E12" s="54">
+      <c r="E12" s="71">
         <v>276385</v>
       </c>
-      <c r="F12" s="60">
+      <c r="F12" s="72">
         <f t="shared" si="0"/>
         <v>3776</v>
       </c>
@@ -3630,11 +5776,11 @@
       <c r="A13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="51"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="60"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="72"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
@@ -3644,7 +5790,7 @@
         <v>53</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D14" s="23">
         <v>107714</v>
@@ -3665,7 +5811,7 @@
         <v>56</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D15" s="23">
         <v>4329319</v>
@@ -3686,7 +5832,7 @@
         <v>59</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D16" s="23">
         <v>579</v>
@@ -3701,16 +5847,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="F12:F13"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="F12:F13"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3718,11 +5864,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5327bade-6e9b-4e0f-a44d-50f3f2085163" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3876,26 +6023,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5327bade-6e9b-4e0f-a44d-50f3f2085163" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AD85119-5E00-43F6-B1C9-7EB5F4C7E743}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A69D0B2-63B4-46AC-AF54-8B9EB6609541}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5327bade-6e9b-4e0f-a44d-50f3f2085163"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3919,9 +6057,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A69D0B2-63B4-46AC-AF54-8B9EB6609541}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AD85119-5E00-43F6-B1C9-7EB5F4C7E743}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="5327bade-6e9b-4e0f-a44d-50f3f2085163"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>